--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/174.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/174.xlsx
@@ -426,13 +426,13 @@
         <v>-2.977924594424187</v>
       </c>
       <c r="E2">
-        <v>-8.329147334957559</v>
+        <v>-7.449781081304084</v>
       </c>
       <c r="F2">
-        <v>-4.04056576864999</v>
+        <v>-3.011980450690377</v>
       </c>
       <c r="G2">
-        <v>-12.98716867431748</v>
+        <v>-11.20973346373724</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-3.041980619666152</v>
       </c>
       <c r="E3">
-        <v>-8.494663059937912</v>
+        <v>-6.988990737127595</v>
       </c>
       <c r="F3">
-        <v>-3.776134391949065</v>
+        <v>-3.433873371739784</v>
       </c>
       <c r="G3">
-        <v>-12.87740753696295</v>
+        <v>-11.63822068343065</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-3.039787175814047</v>
       </c>
       <c r="E4">
-        <v>-9.483156480228228</v>
+        <v>-9.167395044621388</v>
       </c>
       <c r="F4">
-        <v>-4.019252254440006</v>
+        <v>-3.142294108236397</v>
       </c>
       <c r="G4">
-        <v>-12.84228595933682</v>
+        <v>-9.960406409218162</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-2.922716163343493</v>
       </c>
       <c r="E5">
-        <v>-10.13319628165927</v>
+        <v>-7.145558197468789</v>
       </c>
       <c r="F5">
-        <v>-3.916160126021517</v>
+        <v>-2.879687952603016</v>
       </c>
       <c r="G5">
-        <v>-12.48719684479459</v>
+        <v>-10.21552698011102</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-2.654381253748987</v>
       </c>
       <c r="E6">
-        <v>-10.95076245053007</v>
+        <v>-8.419897954071274</v>
       </c>
       <c r="F6">
-        <v>-3.876357637101735</v>
+        <v>-3.055221957005536</v>
       </c>
       <c r="G6">
-        <v>-11.69782043477415</v>
+        <v>-10.48982885185841</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-2.206178828290235</v>
       </c>
       <c r="E7">
-        <v>-10.32152645869026</v>
+        <v>-9.783806398071471</v>
       </c>
       <c r="F7">
-        <v>-3.921300835423033</v>
+        <v>-2.888298561665261</v>
       </c>
       <c r="G7">
-        <v>-11.26934314671736</v>
+        <v>-10.16151874018335</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-1.572382425681005</v>
       </c>
       <c r="E8">
-        <v>-12.16140469174066</v>
+        <v>-11.58828554980391</v>
       </c>
       <c r="F8">
-        <v>-3.722273345617927</v>
+        <v>-3.186641041280532</v>
       </c>
       <c r="G8">
-        <v>-11.35119969572138</v>
+        <v>-9.573185139671768</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-0.7646074420132892</v>
       </c>
       <c r="E9">
-        <v>-13.1212781563025</v>
+        <v>-11.146138933117</v>
       </c>
       <c r="F9">
-        <v>-3.563272439119638</v>
+        <v>-3.124177304416727</v>
       </c>
       <c r="G9">
-        <v>-10.1061465554935</v>
+        <v>-8.029543965620398</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>0.1801243450396453</v>
       </c>
       <c r="E10">
-        <v>-13.35607953360021</v>
+        <v>-11.38143844255555</v>
       </c>
       <c r="F10">
-        <v>-3.729494252739373</v>
+        <v>-3.212582144175431</v>
       </c>
       <c r="G10">
-        <v>-11.08209538047064</v>
+        <v>-8.299952635813609</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>1.197457814414216</v>
       </c>
       <c r="E11">
-        <v>-13.71130209170989</v>
+        <v>-12.3407866041325</v>
       </c>
       <c r="F11">
-        <v>-3.59624757183796</v>
+        <v>-2.760823696972666</v>
       </c>
       <c r="G11">
-        <v>-10.08787234411672</v>
+        <v>-8.806310507681754</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>2.20854398158487</v>
       </c>
       <c r="E12">
-        <v>-13.80735102541258</v>
+        <v>-12.27794044185405</v>
       </c>
       <c r="F12">
-        <v>-3.576630206663411</v>
+        <v>-2.719949831001089</v>
       </c>
       <c r="G12">
-        <v>-8.970652609342254</v>
+        <v>-8.155149373925887</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>3.13078381139854</v>
       </c>
       <c r="E13">
-        <v>-14.73884907184235</v>
+        <v>-13.16725575290238</v>
       </c>
       <c r="F13">
-        <v>-3.290236788180131</v>
+        <v>-2.589679725367745</v>
       </c>
       <c r="G13">
-        <v>-9.092510480097287</v>
+        <v>-7.401884394647817</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>3.883895013802995</v>
       </c>
       <c r="E14">
-        <v>-16.25394514906263</v>
+        <v>-15.81384540262719</v>
       </c>
       <c r="F14">
-        <v>-3.164987822151686</v>
+        <v>-2.607985782044309</v>
       </c>
       <c r="G14">
-        <v>-8.824889289248144</v>
+        <v>-7.069988962153724</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>4.403985179962382</v>
       </c>
       <c r="E15">
-        <v>-16.83328188581192</v>
+        <v>-15.04474296258648</v>
       </c>
       <c r="F15">
-        <v>-3.401243486911028</v>
+        <v>-2.669903140367288</v>
       </c>
       <c r="G15">
-        <v>-8.147538429731103</v>
+        <v>-6.131555239227599</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>4.653112448539869</v>
       </c>
       <c r="E16">
-        <v>-17.70886233519498</v>
+        <v>-16.30615845437107</v>
       </c>
       <c r="F16">
-        <v>-2.74516084546897</v>
+        <v>-1.926538506660573</v>
       </c>
       <c r="G16">
-        <v>-7.798636724801773</v>
+        <v>-6.668999133709502</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>4.623482302856477</v>
       </c>
       <c r="E17">
-        <v>-18.39535182391376</v>
+        <v>-17.08163245734058</v>
       </c>
       <c r="F17">
-        <v>-3.047673222759594</v>
+        <v>-2.133663484811322</v>
       </c>
       <c r="G17">
-        <v>-7.35458663052825</v>
+        <v>-5.310536634942806</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>4.341002913311997</v>
       </c>
       <c r="E18">
-        <v>-18.92661428059762</v>
+        <v>-16.79706315069857</v>
       </c>
       <c r="F18">
-        <v>-2.935517545387045</v>
+        <v>-2.119770424668129</v>
       </c>
       <c r="G18">
-        <v>-6.989099092447172</v>
+        <v>-5.106858631184685</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>3.857333285192213</v>
       </c>
       <c r="E19">
-        <v>-20.86232408059833</v>
+        <v>-19.02793888651924</v>
       </c>
       <c r="F19">
-        <v>-2.051794599365637</v>
+        <v>-1.784221150128481</v>
       </c>
       <c r="G19">
-        <v>-6.281225003058049</v>
+        <v>-5.533263517733892</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>3.236205549942432</v>
       </c>
       <c r="E20">
-        <v>-20.72069605600844</v>
+        <v>-18.76768748529842</v>
       </c>
       <c r="F20">
-        <v>-2.176293680643121</v>
+        <v>-1.361724837125291</v>
       </c>
       <c r="G20">
-        <v>-5.997216611789513</v>
+        <v>-5.475544156256699</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>2.544609499058287</v>
       </c>
       <c r="E21">
-        <v>-20.91743560927168</v>
+        <v>-18.7163119476814</v>
       </c>
       <c r="F21">
-        <v>-1.656274341073085</v>
+        <v>-1.388365938034814</v>
       </c>
       <c r="G21">
-        <v>-6.995935368985767</v>
+        <v>-6.066906905936711</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>1.844535223217368</v>
       </c>
       <c r="E22">
-        <v>-22.19322447755662</v>
+        <v>-20.76003490971307</v>
       </c>
       <c r="F22">
-        <v>-1.589886972803779</v>
+        <v>-0.6704997614196323</v>
       </c>
       <c r="G22">
-        <v>-6.632626169869529</v>
+        <v>-6.197339089638457</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>1.189110522673001</v>
       </c>
       <c r="E23">
-        <v>-21.96613509149397</v>
+        <v>-20.44958990259124</v>
       </c>
       <c r="F23">
-        <v>-1.25725171714854</v>
+        <v>-0.6575434633254221</v>
       </c>
       <c r="G23">
-        <v>-7.705934828611101</v>
+        <v>-6.029563952253732</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>0.6209613638433312</v>
       </c>
       <c r="E24">
-        <v>-21.04759753767415</v>
+        <v>-19.62244148272021</v>
       </c>
       <c r="F24">
-        <v>-1.713336057059326</v>
+        <v>-0.7705685952455469</v>
       </c>
       <c r="G24">
-        <v>-7.240250319238441</v>
+        <v>-5.606251115238204</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>0.1690259420715705</v>
       </c>
       <c r="E25">
-        <v>-21.91618602318937</v>
+        <v>-22.32533364978239</v>
       </c>
       <c r="F25">
-        <v>-1.604643152670886</v>
+        <v>-0.6864175895757142</v>
       </c>
       <c r="G25">
-        <v>-7.537070521743956</v>
+        <v>-6.270373034780318</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-0.1494167646286137</v>
       </c>
       <c r="E26">
-        <v>-21.65595726433859</v>
+        <v>-20.90164029193293</v>
       </c>
       <c r="F26">
-        <v>-1.460770596929832</v>
+        <v>-0.5989748511606405</v>
       </c>
       <c r="G26">
-        <v>-7.938358299286714</v>
+        <v>-6.390473005853998</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-0.3277688676605992</v>
       </c>
       <c r="E27">
-        <v>-22.75107813361351</v>
+        <v>-20.88258447330865</v>
       </c>
       <c r="F27">
-        <v>-1.494515410723058</v>
+        <v>-0.5221247297609836</v>
       </c>
       <c r="G27">
-        <v>-8.009170868371724</v>
+        <v>-7.227723214917839</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-0.3687870418815393</v>
       </c>
       <c r="E28">
-        <v>-21.85892799783639</v>
+        <v>-20.29225713014275</v>
       </c>
       <c r="F28">
-        <v>-1.79792099814999</v>
+        <v>-0.6085174711541209</v>
       </c>
       <c r="G28">
-        <v>-8.323076796405418</v>
+        <v>-6.976807036859857</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-0.2809248731849839</v>
       </c>
       <c r="E29">
-        <v>-22.48730357961473</v>
+        <v>-19.53704351988356</v>
       </c>
       <c r="F29">
-        <v>-1.688167010798205</v>
+        <v>-0.4971805697398546</v>
       </c>
       <c r="G29">
-        <v>-8.410233528817811</v>
+        <v>-7.29926079347595</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-0.07766887637628916</v>
       </c>
       <c r="E30">
-        <v>-21.94184888539084</v>
+        <v>-19.55476343867558</v>
       </c>
       <c r="F30">
-        <v>-1.618618565521682</v>
+        <v>-0.6277903802920612</v>
       </c>
       <c r="G30">
-        <v>-8.153835087346796</v>
+        <v>-7.692295380989304</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>0.2232149980631746</v>
       </c>
       <c r="E31">
-        <v>-22.55300720899202</v>
+        <v>-19.26863180850093</v>
       </c>
       <c r="F31">
-        <v>-1.556275982160408</v>
+        <v>-0.8177875789673318</v>
       </c>
       <c r="G31">
-        <v>-8.15650007650591</v>
+        <v>-7.249106028555992</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>0.6006740124532128</v>
       </c>
       <c r="E32">
-        <v>-21.07137202621442</v>
+        <v>-19.38968697567397</v>
       </c>
       <c r="F32">
-        <v>-1.942946491797484</v>
+        <v>-0.829729513422703</v>
       </c>
       <c r="G32">
-        <v>-8.515843242066101</v>
+        <v>-6.92578490900861</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>1.032163582520146</v>
       </c>
       <c r="E33">
-        <v>-20.27454173982474</v>
+        <v>-20.23609952397363</v>
       </c>
       <c r="F33">
-        <v>-1.78746141243147</v>
+        <v>-0.8514310355819696</v>
       </c>
       <c r="G33">
-        <v>-7.668492558561944</v>
+        <v>-7.176462727787764</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>1.495429459389813</v>
       </c>
       <c r="E34">
-        <v>-20.99279394523332</v>
+        <v>-18.72237104590367</v>
       </c>
       <c r="F34">
-        <v>-1.740803060603751</v>
+        <v>-0.6537995825413233</v>
       </c>
       <c r="G34">
-        <v>-8.446202606101991</v>
+        <v>-6.869214306833544</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>1.966945579019796</v>
       </c>
       <c r="E35">
-        <v>-19.58791186841173</v>
+        <v>-19.62827415724209</v>
       </c>
       <c r="F35">
-        <v>-1.729919833552851</v>
+        <v>-0.5372689175773733</v>
       </c>
       <c r="G35">
-        <v>-7.227259738542341</v>
+        <v>-6.574330773468502</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>2.423897041250852</v>
       </c>
       <c r="E36">
-        <v>-19.23009902316966</v>
+        <v>-18.33927120180277</v>
       </c>
       <c r="F36">
-        <v>-1.825482232196382</v>
+        <v>-0.1948954542480964</v>
       </c>
       <c r="G36">
-        <v>-6.799408143592472</v>
+        <v>-6.281248176876824</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>2.848764741458206</v>
       </c>
       <c r="E37">
-        <v>-18.51799195698949</v>
+        <v>-17.07282910386966</v>
       </c>
       <c r="F37">
-        <v>-1.680486037108324</v>
+        <v>-0.2601845224650453</v>
       </c>
       <c r="G37">
-        <v>-7.039879550474052</v>
+        <v>-5.493133084706847</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>3.226051724315284</v>
       </c>
       <c r="E38">
-        <v>-18.01874128306585</v>
+        <v>-17.11403821733946</v>
       </c>
       <c r="F38">
-        <v>-1.66155124918333</v>
+        <v>-0.6814415855894034</v>
       </c>
       <c r="G38">
-        <v>-6.618020042950264</v>
+        <v>-5.991615168737066</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>3.545881363603258</v>
       </c>
       <c r="E39">
-        <v>-18.2670827976465</v>
+        <v>-17.15184191835549</v>
       </c>
       <c r="F39">
-        <v>-1.704543321816807</v>
+        <v>-0.4601361046718105</v>
       </c>
       <c r="G39">
-        <v>-6.318481882557007</v>
+        <v>-5.766405376791527</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>3.808128742811961</v>
       </c>
       <c r="E40">
-        <v>-18.00269689965668</v>
+        <v>-15.72951615965635</v>
       </c>
       <c r="F40">
-        <v>-1.65264052785011</v>
+        <v>-0.6807653431635108</v>
       </c>
       <c r="G40">
-        <v>-6.42394262125603</v>
+        <v>-5.947627950156771</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>4.014680799402504</v>
       </c>
       <c r="E41">
-        <v>-17.29399071745627</v>
+        <v>-16.05026344514564</v>
       </c>
       <c r="F41">
-        <v>-1.623467081181799</v>
+        <v>-0.4883783322618421</v>
       </c>
       <c r="G41">
-        <v>-7.433510036184475</v>
+        <v>-6.001543494809341</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>4.169195700260238</v>
       </c>
       <c r="E42">
-        <v>-17.82318818999262</v>
+        <v>-16.9324599950539</v>
       </c>
       <c r="F42">
-        <v>-1.706176122615625</v>
+        <v>-0.5993977006400628</v>
       </c>
       <c r="G42">
-        <v>-6.718855949530925</v>
+        <v>-6.689067660768563</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>4.28033272678663</v>
       </c>
       <c r="E43">
-        <v>-17.26398504868144</v>
+        <v>-14.79717128858714</v>
       </c>
       <c r="F43">
-        <v>-1.626934605283654</v>
+        <v>-0.7039658429717409</v>
       </c>
       <c r="G43">
-        <v>-7.021320632180898</v>
+        <v>-6.65278739220369</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>4.354424307837221</v>
       </c>
       <c r="E44">
-        <v>-16.33500483379993</v>
+        <v>-14.63260201467439</v>
       </c>
       <c r="F44">
-        <v>-1.2992215076136</v>
+        <v>-0.6297628860097411</v>
       </c>
       <c r="G44">
-        <v>-6.459521054166578</v>
+        <v>-6.402076467969144</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>4.396418538871446</v>
       </c>
       <c r="E45">
-        <v>-15.57746811637481</v>
+        <v>-13.34157935982765</v>
       </c>
       <c r="F45">
-        <v>-1.835475416522805</v>
+        <v>-0.8260545238459257</v>
       </c>
       <c r="G45">
-        <v>-6.832841342993571</v>
+        <v>-6.040227219435724</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>4.411070848209016</v>
       </c>
       <c r="E46">
-        <v>-15.74412501680509</v>
+        <v>-13.63482975114236</v>
       </c>
       <c r="F46">
-        <v>-2.103522393828678</v>
+        <v>-0.8166956137386363</v>
       </c>
       <c r="G46">
-        <v>-7.47537188452856</v>
+        <v>-5.732872861024249</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>4.39679061800214</v>
       </c>
       <c r="E47">
-        <v>-15.08011487306039</v>
+        <v>-14.52858749519221</v>
       </c>
       <c r="F47">
-        <v>-1.930249921473406</v>
+        <v>-1.17303023656547</v>
       </c>
       <c r="G47">
-        <v>-7.668115156370467</v>
+        <v>-5.614699627454424</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>4.348692967881763</v>
       </c>
       <c r="E48">
-        <v>-14.08537215863949</v>
+        <v>-13.68140510631125</v>
       </c>
       <c r="F48">
-        <v>-1.641769178593576</v>
+        <v>-1.085183653141959</v>
       </c>
       <c r="G48">
-        <v>-7.193872886778791</v>
+        <v>-6.366795984157131</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>4.260116594562477</v>
       </c>
       <c r="E49">
-        <v>-14.22272983224015</v>
+        <v>-11.68706515333322</v>
       </c>
       <c r="F49">
-        <v>-1.980875456619301</v>
+        <v>-0.9571220254076943</v>
       </c>
       <c r="G49">
-        <v>-7.382014500321112</v>
+        <v>-6.496963324215735</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>4.122870317452262</v>
       </c>
       <c r="E50">
-        <v>-13.96617366580959</v>
+        <v>-11.9760451936587</v>
       </c>
       <c r="F50">
-        <v>-2.037308441357113</v>
+        <v>-1.489407167292808</v>
       </c>
       <c r="G50">
-        <v>-7.602980172885307</v>
+        <v>-7.385646168777693</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>3.933311905811006</v>
       </c>
       <c r="E51">
-        <v>-12.59362942187677</v>
+        <v>-12.12454291331822</v>
       </c>
       <c r="F51">
-        <v>-1.883484669496394</v>
+        <v>-1.608098007125417</v>
       </c>
       <c r="G51">
-        <v>-7.551865349758959</v>
+        <v>-6.9083846816542</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>3.690100965884472</v>
       </c>
       <c r="E52">
-        <v>-13.47065898294228</v>
+        <v>-12.3155177191697</v>
       </c>
       <c r="F52">
-        <v>-2.092210774327652</v>
+        <v>-0.8880011807283397</v>
       </c>
       <c r="G52">
-        <v>-7.881900255659983</v>
+        <v>-6.901750348393501</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>3.39321369033698</v>
       </c>
       <c r="E53">
-        <v>-12.32483731867748</v>
+        <v>-10.56690635126989</v>
       </c>
       <c r="F53">
-        <v>-2.310821579630125</v>
+        <v>-1.129934431194531</v>
       </c>
       <c r="G53">
-        <v>-8.362909280333929</v>
+        <v>-6.36843470419907</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>3.048824866289358</v>
       </c>
       <c r="E54">
-        <v>-11.65676060527389</v>
+        <v>-11.45460499709748</v>
       </c>
       <c r="F54">
-        <v>-2.148102131642383</v>
+        <v>-1.338586893700721</v>
       </c>
       <c r="G54">
-        <v>-7.854296926953539</v>
+        <v>-7.091543924159919</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>2.664281179687253</v>
       </c>
       <c r="E55">
-        <v>-12.36671664630042</v>
+        <v>-10.89174737726211</v>
       </c>
       <c r="F55">
-        <v>-1.980793895764656</v>
+        <v>-1.576274228607619</v>
       </c>
       <c r="G55">
-        <v>-8.561720782149321</v>
+        <v>-7.264480202040366</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>2.248357208827192</v>
       </c>
       <c r="E56">
-        <v>-11.68490054275756</v>
+        <v>-10.73681016756368</v>
       </c>
       <c r="F56">
-        <v>-2.339987899621815</v>
+        <v>-1.412744715044131</v>
       </c>
       <c r="G56">
-        <v>-8.601361254436554</v>
+        <v>-6.553245908928885</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>1.816505584502139</v>
       </c>
       <c r="E57">
-        <v>-11.03833860936441</v>
+        <v>-11.25364490605909</v>
       </c>
       <c r="F57">
-        <v>-2.249753879530779</v>
+        <v>-1.48231533220347</v>
       </c>
       <c r="G57">
-        <v>-8.744777397743322</v>
+        <v>-7.098539106884399</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>1.384217536916795</v>
       </c>
       <c r="E58">
-        <v>-11.66554131637477</v>
+        <v>-10.0459552299015</v>
       </c>
       <c r="F58">
-        <v>-2.546406544934277</v>
+        <v>-1.665463002794465</v>
       </c>
       <c r="G58">
-        <v>-9.200841461778859</v>
+        <v>-7.847503687506955</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>0.9658073647688058</v>
       </c>
       <c r="E59">
-        <v>-10.96245949889188</v>
+        <v>-8.884917892970927</v>
       </c>
       <c r="F59">
-        <v>-2.407159202319264</v>
+        <v>-1.774769593225138</v>
       </c>
       <c r="G59">
-        <v>-7.993031958867777</v>
+        <v>-7.301700665538393</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>0.5778827180450726</v>
       </c>
       <c r="E60">
-        <v>-11.40094710858059</v>
+        <v>-8.738516856776952</v>
       </c>
       <c r="F60">
-        <v>-2.756356854438169</v>
+        <v>-1.48973974553505</v>
       </c>
       <c r="G60">
-        <v>-8.867347035789297</v>
+        <v>-7.539358108711593</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>0.2325314756193719</v>
       </c>
       <c r="E61">
-        <v>-10.55064460110835</v>
+        <v>-9.229249471092158</v>
       </c>
       <c r="F61">
-        <v>-2.720797905518808</v>
+        <v>-1.587086188892325</v>
       </c>
       <c r="G61">
-        <v>-8.588860634480266</v>
+        <v>-7.736074035200626</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-0.06358479317611364</v>
       </c>
       <c r="E62">
-        <v>-10.53162953875014</v>
+        <v>-10.14852969464924</v>
       </c>
       <c r="F62">
-        <v>-2.390041716932236</v>
+        <v>-1.551429050206205</v>
       </c>
       <c r="G62">
-        <v>-9.093881045950546</v>
+        <v>-7.337070534079966</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-0.3033626507394051</v>
       </c>
       <c r="E63">
-        <v>-9.925244226753039</v>
+        <v>-8.767689286334365</v>
       </c>
       <c r="F63">
-        <v>-2.42083925401683</v>
+        <v>-1.837030615731767</v>
       </c>
       <c r="G63">
-        <v>-8.676659612727278</v>
+        <v>-8.184457633585055</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-0.4844403016614245</v>
       </c>
       <c r="E64">
-        <v>-9.515385629740818</v>
+        <v>-7.740527226492552</v>
       </c>
       <c r="F64">
-        <v>-2.373109525137316</v>
+        <v>-1.621946723502978</v>
       </c>
       <c r="G64">
-        <v>-9.509433964222023</v>
+        <v>-6.808081772905362</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-0.6084702864312251</v>
       </c>
       <c r="E65">
-        <v>-9.369659336173985</v>
+        <v>-8.193003292390959</v>
       </c>
       <c r="F65">
-        <v>-2.255683274478185</v>
+        <v>-1.835667836791531</v>
       </c>
       <c r="G65">
-        <v>-8.784950867862378</v>
+        <v>-8.352547272796009</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-0.6760641281837447</v>
       </c>
       <c r="E66">
-        <v>-11.08437507612638</v>
+        <v>-8.686905838511533</v>
       </c>
       <c r="F66">
-        <v>-2.604755813829771</v>
+        <v>-2.011098900309547</v>
       </c>
       <c r="G66">
-        <v>-9.144317207241343</v>
+        <v>-8.700078411872081</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-0.6899578533610301</v>
       </c>
       <c r="E67">
-        <v>-10.05727188644667</v>
+        <v>-7.56682854898034</v>
       </c>
       <c r="F67">
-        <v>-2.672774399191979</v>
+        <v>-1.735361447078301</v>
       </c>
       <c r="G67">
-        <v>-8.770930707503563</v>
+        <v>-8.153424579699927</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-0.6548176789962398</v>
       </c>
       <c r="E68">
-        <v>-9.700835697302935</v>
+        <v>-8.094753520320543</v>
       </c>
       <c r="F68">
-        <v>-2.557981059617267</v>
+        <v>-1.88111782100577</v>
       </c>
       <c r="G68">
-        <v>-9.318140711326317</v>
+        <v>-7.734385656975598</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-0.5757867647544082</v>
       </c>
       <c r="E69">
-        <v>-9.962730934588533</v>
+        <v>-8.988814672128909</v>
       </c>
       <c r="F69">
-        <v>-2.511523838440808</v>
+        <v>-1.864283027124649</v>
       </c>
       <c r="G69">
-        <v>-9.503137306606328</v>
+        <v>-7.724457330903324</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-0.4605104420057713</v>
       </c>
       <c r="E70">
-        <v>-9.628361999284177</v>
+        <v>-7.557934626029275</v>
       </c>
       <c r="F70">
-        <v>-2.726439857842561</v>
+        <v>-1.856460311755336</v>
       </c>
       <c r="G70">
-        <v>-9.621966028192929</v>
+        <v>-7.330068730264408</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-0.3189468615677367</v>
       </c>
       <c r="E71">
-        <v>-10.07467028358414</v>
+        <v>-8.874742411875692</v>
       </c>
       <c r="F71">
-        <v>-2.691789956118661</v>
+        <v>-1.826943992756333</v>
       </c>
       <c r="G71">
-        <v>-9.921643231498836</v>
+        <v>-8.670756910030757</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-0.1617975665462355</v>
       </c>
       <c r="E72">
-        <v>-10.82249795273681</v>
+        <v>-8.414961917402913</v>
       </c>
       <c r="F72">
-        <v>-2.554728919519912</v>
+        <v>-2.077237626750129</v>
       </c>
       <c r="G72">
-        <v>-9.726993085426308</v>
+        <v>-8.135349001055506</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-0.0003186161603355308</v>
       </c>
       <c r="E73">
-        <v>-9.478890657713002</v>
+        <v>-9.367517367968357</v>
       </c>
       <c r="F73">
-        <v>-2.61996255802982</v>
+        <v>-1.240816017158109</v>
       </c>
       <c r="G73">
-        <v>-9.564034791801223</v>
+        <v>-8.142198519776258</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>0.154506926963958</v>
       </c>
       <c r="E74">
-        <v>-10.27388691212957</v>
+        <v>-9.346156556074176</v>
       </c>
       <c r="F74">
-        <v>-2.452187920759996</v>
+        <v>-1.950319434686812</v>
       </c>
       <c r="G74">
-        <v>-9.648937042701371</v>
+        <v>-7.811246592760857</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>0.2919847910354447</v>
       </c>
       <c r="E75">
-        <v>-10.70148807030385</v>
+        <v>-9.808509223783313</v>
       </c>
       <c r="F75">
-        <v>-2.666445118500925</v>
+        <v>-1.80352573338473</v>
       </c>
       <c r="G75">
-        <v>-9.033827749868166</v>
+        <v>-7.617804795810163</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>0.4028772057610543</v>
       </c>
       <c r="E76">
-        <v>-11.60012298085996</v>
+        <v>-9.954407599362437</v>
       </c>
       <c r="F76">
-        <v>-3.096763355020471</v>
+        <v>-1.978554535600224</v>
       </c>
       <c r="G76">
-        <v>-9.159651654179246</v>
+        <v>-8.729648204628852</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>0.4797723452149678</v>
       </c>
       <c r="E77">
-        <v>-11.59486995101106</v>
+        <v>-11.51041391076801</v>
       </c>
       <c r="F77">
-        <v>-2.916172577629953</v>
+        <v>-2.127770515099972</v>
       </c>
       <c r="G77">
-        <v>-9.837194525337567</v>
+        <v>-7.411587603623421</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>0.5175759535118427</v>
       </c>
       <c r="E78">
-        <v>-12.69383096624449</v>
+        <v>-11.52933387517206</v>
       </c>
       <c r="F78">
-        <v>-2.891563371409939</v>
+        <v>-1.851863605335773</v>
       </c>
       <c r="G78">
-        <v>-9.670160950153639</v>
+        <v>-8.312393665950189</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>0.5134664801325045</v>
       </c>
       <c r="E79">
-        <v>-12.6921871301797</v>
+        <v>-10.1447257764828</v>
       </c>
       <c r="F79">
-        <v>-2.903900440491212</v>
+        <v>-2.187356658315423</v>
       </c>
       <c r="G79">
-        <v>-9.843567325500663</v>
+        <v>-7.420936584226324</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>0.4661149965365223</v>
       </c>
       <c r="E80">
-        <v>-13.23583949174855</v>
+        <v>-11.04540302881637</v>
       </c>
       <c r="F80">
-        <v>-2.858912106551324</v>
+        <v>-1.911698390379948</v>
       </c>
       <c r="G80">
-        <v>-9.984798508751512</v>
+        <v>-7.834864024638017</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>0.3757195111449821</v>
       </c>
       <c r="E81">
-        <v>-13.56814797137941</v>
+        <v>-12.80301700304343</v>
       </c>
       <c r="F81">
-        <v>-3.171762124204978</v>
+        <v>-2.204732287766667</v>
       </c>
       <c r="G81">
-        <v>-9.71017551408681</v>
+        <v>-7.622379969745436</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>0.2432012097847534</v>
       </c>
       <c r="E82">
-        <v>-14.34823648936273</v>
+        <v>-13.11231177776731</v>
       </c>
       <c r="F82">
-        <v>-3.203406943954332</v>
+        <v>-2.382097848060392</v>
       </c>
       <c r="G82">
-        <v>-9.388671884040489</v>
+        <v>-7.422942774823121</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>0.06776892570473179</v>
       </c>
       <c r="E83">
-        <v>-15.12608341271225</v>
+        <v>-14.08527253221132</v>
       </c>
       <c r="F83">
-        <v>-2.855705102072559</v>
+        <v>-2.625535619146251</v>
       </c>
       <c r="G83">
-        <v>-10.0468083372476</v>
+        <v>-7.712383771321601</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-0.1504181212448796</v>
       </c>
       <c r="E84">
-        <v>-16.64262407314098</v>
+        <v>-14.7977373478381</v>
       </c>
       <c r="F84">
-        <v>-2.766586802798951</v>
+        <v>-2.343370695457194</v>
       </c>
       <c r="G84">
-        <v>-9.562204060118006</v>
+        <v>-8.239045218982097</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-0.4104069470943484</v>
       </c>
       <c r="E85">
-        <v>-17.93704761196748</v>
+        <v>-15.39100367063498</v>
       </c>
       <c r="F85">
-        <v>-2.878848588467833</v>
+        <v>-2.323469055070824</v>
       </c>
       <c r="G85">
-        <v>-9.959797268838935</v>
+        <v>-8.290656623939336</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-0.7126941017078976</v>
       </c>
       <c r="E86">
-        <v>-17.99988471729792</v>
+        <v>-16.03336318014901</v>
       </c>
       <c r="F86">
-        <v>-3.185639347289017</v>
+        <v>-2.359895082978889</v>
       </c>
       <c r="G86">
-        <v>-9.640015122473036</v>
+        <v>-7.278662579130605</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-1.053573655821012</v>
       </c>
       <c r="E87">
-        <v>-18.39678282170019</v>
+        <v>-18.01142779754347</v>
       </c>
       <c r="F87">
-        <v>-3.577179752616069</v>
+        <v>-2.558467257333306</v>
       </c>
       <c r="G87">
-        <v>-9.629053906192508</v>
+        <v>-7.547028642726084</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-1.425760363014334</v>
       </c>
       <c r="E88">
-        <v>-21.12386156843733</v>
+        <v>-19.45563061417367</v>
       </c>
       <c r="F88">
-        <v>-3.214805667280707</v>
+        <v>-2.541055202646007</v>
       </c>
       <c r="G88">
-        <v>-9.722652960224323</v>
+        <v>-6.815652990553676</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-1.822483433165951</v>
       </c>
       <c r="E89">
-        <v>-22.44577294449039</v>
+        <v>-20.23960003438156</v>
       </c>
       <c r="F89">
-        <v>-3.149048613965746</v>
+        <v>-2.747281427689744</v>
       </c>
       <c r="G89">
-        <v>-9.572069485825034</v>
+        <v>-8.0684230124336</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.232382834818373</v>
       </c>
       <c r="E90">
-        <v>-23.52061077868495</v>
+        <v>-21.83504935439394</v>
       </c>
       <c r="F90">
-        <v>-3.031722136779288</v>
+        <v>-2.603848350340224</v>
       </c>
       <c r="G90">
-        <v>-9.34714771134141</v>
+        <v>-8.283578677576374</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-2.641079949251412</v>
       </c>
       <c r="E91">
-        <v>-24.66381498497332</v>
+        <v>-24.7650535498888</v>
       </c>
       <c r="F91">
-        <v>-2.991811955857256</v>
+        <v>-2.705430415168341</v>
       </c>
       <c r="G91">
-        <v>-9.5935714791026</v>
+        <v>-7.184619911996528</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.03620236106087</v>
       </c>
       <c r="E92">
-        <v>-27.43388706393929</v>
+        <v>-24.27677084001174</v>
       </c>
       <c r="F92">
-        <v>-2.995295317018265</v>
+        <v>-1.992292392563704</v>
       </c>
       <c r="G92">
-        <v>-9.816447336442954</v>
+        <v>-7.258534462251836</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-3.402158810861904</v>
       </c>
       <c r="E93">
-        <v>-29.21085120760112</v>
+        <v>-27.59549924432503</v>
       </c>
       <c r="F93">
-        <v>-3.029556418939924</v>
+        <v>-2.200020762668235</v>
       </c>
       <c r="G93">
-        <v>-10.57952477269942</v>
+        <v>-7.490428245641165</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-3.723236114826169</v>
       </c>
       <c r="E94">
-        <v>-31.98550836649985</v>
+        <v>-29.29099161211486</v>
       </c>
       <c r="F94">
-        <v>-2.976276592679753</v>
+        <v>-2.58844839401849</v>
       </c>
       <c r="G94">
-        <v>-9.926205163251952</v>
+        <v>-7.851221430147556</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-3.989826954047142</v>
       </c>
       <c r="E95">
-        <v>-34.01765881320492</v>
+        <v>-31.89324297283057</v>
       </c>
       <c r="F95">
-        <v>-2.788947938471998</v>
+        <v>-2.586342857003914</v>
       </c>
       <c r="G95">
-        <v>-10.39135336424725</v>
+        <v>-8.47046890490485</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-4.190307488959387</v>
       </c>
       <c r="E96">
-        <v>-35.84427314588685</v>
+        <v>-35.04693793464532</v>
       </c>
       <c r="F96">
-        <v>-2.337287681035991</v>
+        <v>-2.376633270799168</v>
       </c>
       <c r="G96">
-        <v>-9.973512859008137</v>
+        <v>-8.432467152659555</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.319397588801853</v>
       </c>
       <c r="E97">
-        <v>-38.66846954619249</v>
+        <v>-37.32788047909479</v>
       </c>
       <c r="F97">
-        <v>-2.65854005042401</v>
+        <v>-2.087424815051194</v>
       </c>
       <c r="G97">
-        <v>-10.19108191184904</v>
+        <v>-9.199487448653297</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.373916629456267</v>
       </c>
       <c r="E98">
-        <v>-41.29722380103809</v>
+        <v>-38.95485703514858</v>
       </c>
       <c r="F98">
-        <v>-2.292815635224536</v>
+        <v>-2.058330553678656</v>
       </c>
       <c r="G98">
-        <v>-10.79020126972756</v>
+        <v>-8.673537768283744</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.362925003154911</v>
       </c>
       <c r="E99">
-        <v>-42.24480245866911</v>
+        <v>-41.78720468866803</v>
       </c>
       <c r="F99">
-        <v>-2.316892716256961</v>
+        <v>-2.383763114830477</v>
       </c>
       <c r="G99">
-        <v>-10.73392530610549</v>
+        <v>-8.708209111716531</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.285820506775344</v>
       </c>
       <c r="E100">
-        <v>-45.79938058201287</v>
+        <v>-44.41206898434104</v>
       </c>
       <c r="F100">
-        <v>-2.172618691066343</v>
+        <v>-1.884929801144233</v>
       </c>
       <c r="G100">
-        <v>-11.16664009245255</v>
+        <v>-9.263913975393054</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.173713292080703</v>
       </c>
       <c r="E101">
-        <v>-47.96845170457686</v>
+        <v>-47.39755377914087</v>
       </c>
       <c r="F101">
-        <v>-2.446956148268342</v>
+        <v>-2.152656078002229</v>
       </c>
       <c r="G101">
-        <v>-11.7930582088479</v>
+        <v>-9.231146195645348</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.019909917366142</v>
       </c>
       <c r="E102">
-        <v>-50.88146619771344</v>
+        <v>-48.82380346056766</v>
       </c>
       <c r="F102">
-        <v>-2.211921520769804</v>
+        <v>-1.989353826237606</v>
       </c>
       <c r="G102">
-        <v>-11.53223025744535</v>
+        <v>-9.623267072589863</v>
       </c>
     </row>
   </sheetData>
